--- a/Testver1.xlsx
+++ b/Testver1.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
@@ -20,8 +20,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -49,8 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -68,8 +77,83 @@
 </styleSheet>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>228600</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>95250</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>19</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>72</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1025" name="Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1025"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri"/>
+                  <a:cs typeface="Calibri"/>
+                </a:rPr>
+                <a:t>Iniciar</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -114,7 +198,7 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -149,7 +233,7 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -330,10 +414,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Hoja1"/>
+  <dimension ref="H59"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="59" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H59" s="1"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1025" r:id="rId4" name="Button 1">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!mod_engine.BootGame">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>228600</xdr:colOff>
+                    <xdr:row>62</xdr:row>
+                    <xdr:rowOff>95250</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>19</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>72</xdr:row>
+                    <xdr:rowOff>161925</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
 </worksheet>
 </file>